--- a/data/trans_bre/IMC_inf_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_R2-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-31,63; -6,48</t>
+          <t>-31,88; -6,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 11,15</t>
+          <t>-17,58; 12,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 21,61</t>
+          <t>-12,19; 21,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 24,69</t>
+          <t>-17,64; 24,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-56,94; -14,42</t>
+          <t>-56,19; -14,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,17; 28,25</t>
+          <t>-31,95; 30,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,58; 51,05</t>
+          <t>-19,87; 50,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,35; 86,42</t>
+          <t>-43,05; 88,69</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,42; -6,87</t>
+          <t>-18,37; -7,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,89; -2,61</t>
+          <t>-14,83; -2,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,21; -3,68</t>
+          <t>-15,64; -4,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,27; -5,44</t>
+          <t>-22,16; -7,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,49; -14,86</t>
+          <t>-36,2; -15,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,37; -5,39</t>
+          <t>-27,22; -5,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,19; -8,87</t>
+          <t>-33,23; -9,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,69; -15,07</t>
+          <t>-48,02; -19,24</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 11,76</t>
+          <t>-6,48; 12,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 1,35</t>
+          <t>-20,01; 1,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,67; -5,36</t>
+          <t>-26,79; -6,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,79; 1,42</t>
+          <t>-16,59; 2,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 40,05</t>
+          <t>-17,34; 44,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,97; 2,79</t>
+          <t>-36,42; 2,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-51,48; -13,46</t>
+          <t>-53,87; -16,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,52; 5,72</t>
+          <t>-47,05; 8,45</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,42; -5,16</t>
+          <t>-14,62; -5,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,83; -3,11</t>
+          <t>-13,69; -3,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,65; -5,35</t>
+          <t>-14,63; -4,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,28; -5,75</t>
+          <t>-16,34; -5,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,69; -11,96</t>
+          <t>-30,91; -13,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,31; -6,54</t>
+          <t>-25,83; -6,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,02; -12,61</t>
+          <t>-31,25; -11,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,7; -15,67</t>
+          <t>-39,66; -14,41</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_R2-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-31,88; -6,82</t>
+          <t>-31,28; -6,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 12,13</t>
+          <t>-18,73; 10,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 21,71</t>
+          <t>-10,56; 22,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 24,71</t>
+          <t>-17,76; 23,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-56,19; -14,49</t>
+          <t>-55,47; -15,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-31,95; 30,59</t>
+          <t>-33,85; 26,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 50,89</t>
+          <t>-18,38; 50,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,05; 88,69</t>
+          <t>-42,82; 92,98</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,37; -7,38</t>
+          <t>-17,55; -6,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,83; -2,74</t>
+          <t>-15,13; -1,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,64; -4,0</t>
+          <t>-15,56; -3,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,16; -7,26</t>
+          <t>-21,84; -6,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,2; -15,68</t>
+          <t>-34,88; -14,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,22; -5,46</t>
+          <t>-27,97; -3,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,23; -9,69</t>
+          <t>-33,35; -9,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,02; -19,24</t>
+          <t>-48,67; -18,38</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 12,41</t>
+          <t>-5,43; 12,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 1,01</t>
+          <t>-21,6; 0,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,79; -6,87</t>
+          <t>-24,87; -6,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 2,11</t>
+          <t>-17,11; 1,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 44,72</t>
+          <t>-15,18; 42,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,42; 2,93</t>
+          <t>-39,07; 1,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-53,87; -16,75</t>
+          <t>-50,74; -15,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 8,45</t>
+          <t>-46,8; 6,4</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,62; -5,7</t>
+          <t>-14,45; -5,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,69; -3,14</t>
+          <t>-13,41; -3,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,63; -4,48</t>
+          <t>-14,87; -5,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,34; -5,19</t>
+          <t>-16,62; -5,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,91; -13,46</t>
+          <t>-30,44; -13,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,83; -6,68</t>
+          <t>-25,02; -7,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,25; -11,01</t>
+          <t>-31,9; -12,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,66; -14,41</t>
+          <t>-40,14; -14,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_R2-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>-0,58</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>-1,61%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-31,28; -6,86</t>
+          <t>-31,63; -6,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 10,58</t>
+          <t>-17,52; 11,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 22,22</t>
+          <t>-10,41; 21,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 23,89</t>
+          <t>-19,57; 16,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-55,47; -15,81</t>
+          <t>-56,94; -14,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,85; 26,7</t>
+          <t>-33,17; 28,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 50,26</t>
+          <t>-16,58; 51,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-42,82; 92,98</t>
+          <t>-42,59; 60,26</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-13,56</t>
+          <t>-12,62</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-32,12%</t>
+          <t>-29,62%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,55; -6,63</t>
+          <t>-18,42; -6,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,13; -1,88</t>
+          <t>-14,89; -2,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,56; -3,94</t>
+          <t>-15,21; -3,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,84; -6,93</t>
+          <t>-18,78; -6,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,88; -14,89</t>
+          <t>-36,49; -14,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,97; -3,97</t>
+          <t>-27,37; -5,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,35; -9,86</t>
+          <t>-32,19; -8,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,67; -18,38</t>
+          <t>-40,97; -15,88</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-7,51</t>
+          <t>-8,54</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-24,45%</t>
+          <t>-27,66%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 12,42</t>
+          <t>-6,31; 11,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,6; 0,95</t>
+          <t>-19,75; 1,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,87; -6,4</t>
+          <t>-24,67; -5,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 1,41</t>
+          <t>-17,88; 0,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 42,58</t>
+          <t>-16,33; 40,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 1,99</t>
+          <t>-36,97; 2,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-50,74; -15,25</t>
+          <t>-51,48; -13,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-46,8; 6,4</t>
+          <t>-50,26; 2,38</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-10,85</t>
+          <t>-10,9</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-27,81%</t>
+          <t>-27,68%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,45; -5,91</t>
+          <t>-14,42; -5,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,41; -3,56</t>
+          <t>-12,83; -3,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,87; -5,13</t>
+          <t>-14,65; -5,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,62; -5,43</t>
+          <t>-15,91; -5,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,44; -13,47</t>
+          <t>-30,69; -11,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,02; -7,43</t>
+          <t>-24,31; -6,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,9; -12,12</t>
+          <t>-31,02; -12,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,14; -14,67</t>
+          <t>-37,81; -15,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_R2-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -522,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as</t>
+          <t>Población con sobrepeso u obesidad declarado por madres/padres</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-19,03</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-2,49</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,77</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-38,03%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-5,31%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,99%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-1,61%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-19.03380771304203</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-2.485352451372874</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>5.7682369926357</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.5785208426045407</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.3803455247355388</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.05305481141406267</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.1099184813895242</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.01613789500639073</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-31,63; -6,48</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-17,52; 11,15</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-10,41; 21,61</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-19,57; 16,98</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-56,94; -14,42</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-33,17; 28,25</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-16,58; 51,05</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-42,59; 60,26</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-31.63193797966476</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-17.51900615016527</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-10.40607587508682</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-19.56779927242644</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.5693820557656569</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.3317372998143778</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.1658422710586418</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.4258888655284503</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>-6.484374667549265</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>11.1453862528073</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>21.60634734678331</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>16.9837096458359</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>-0.1441725314755473</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.2824607297149264</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.5104625848545488</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.6025827537144722</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-12,62</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-8,99</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-9,81</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-12,62</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-26,11%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-17,39%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-22,33%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-29,62%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-18,42; -6,87</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-14,89; -2,61</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-15,21; -3,68</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-18,78; -6,0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-36,49; -14,86</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-27,37; -5,39</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-32,19; -8,87</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-40,97; -15,88</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-12.61898118442599</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-8.985612316085556</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-9.807322277574826</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-12.61687405240968</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2610737850379904</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.173940868796096</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.2233103508969738</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.2961964925769286</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,92</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-9,7</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-15,53</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-8,54</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-19,72%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-35,31%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-27,66%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-18.41682867117488</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-14.89462826103678</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-15.21433269720252</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-18.77708111812941</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3648514060850505</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.273677005745461</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.321871368248202</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.4096833090694185</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-6,31; 11,76</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-19,75; 1,35</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-24,67; -5,36</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-17,88; 0,55</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-16,33; 40,05</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-36,97; 2,79</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-51,48; -13,46</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-50,26; 2,38</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-6.873284283665575</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-2.613642742344913</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>-3.68499949492845</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>-6.002016293053091</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.148633050824404</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.05388052250062687</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>-0.08868169871456623</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>-0.1588065364600281</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-10,18</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-8,39</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-9,85</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-10,9</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-22,41%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-16,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-22,02%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-27,68%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>2.918872642734</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-9.703285448124188</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-15.534032141063</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-8.536399781389111</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.0871951744391655</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1972078267206726</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.3531043855123615</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.2765712152344088</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-14,42; -5,16</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-12,83; -3,11</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-14,65; -5,35</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-15,91; -5,96</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-30,69; -11,96</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-24,31; -6,54</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-31,02; -12,61</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-37,81; -15,74</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-6.30635925804887</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-19.75036962048848</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-24.6688057526848</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-17.88143963344898</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1633396841465928</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.3696645317908285</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.5147697049978508</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.5025548397427642</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>11.7597771137063</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.352281252351155</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-5.35831057808779</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.554256015434876</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.4004898459994314</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.02792859035096378</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>-0.134588337526974</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.02378715189641804</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-10.17690067285283</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-8.386401710005414</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-9.850454737613596</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-10.9004640478858</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2240672304047215</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1659334814439677</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.2202378907336141</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.2768447389256105</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-14.42132587158736</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-12.83458335900293</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-14.65309017052844</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-15.91371171399373</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3068717838752523</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2430632008461235</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.3102486501396552</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3780937200481644</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-5.159110482671275</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-3.107612450742153</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-5.350902873224721</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-5.963093797599904</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.1195547808536363</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.06543043185754255</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>-0.1261108160223352</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>-0.1573693407208534</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
